--- a/docs/reviews/DSS6_Review_Rows_20260924-3f723d0d.xlsx
+++ b/docs/reviews/DSS6_Review_Rows_20260924-3f723d0d.xlsx
@@ -45745,22 +45745,22 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
         <is>
-          <t>The name stamps SATIN-STRIPE-KING-BLUE: 0 in FBA, 0.00/day, but the ad serves SATIN-STRIPE-KING-BLUE--6-PCS: 0 in FBA, 4.80/day, running out YES, and the swap cannot load. The name would describe a child the campaign does not advertise.</t>
+          <t>Naming only.</t>
         </is>
       </c>
       <c r="N537" t="inlineStr">
@@ -64946,22 +64946,22 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>The name stamps SATIN-STRIPE-QUEEN-PINK: 77 in FBA, 2 reserved, 0.53/day, 150 days left, but the ad serves SATIN-STRIPE-QUEEN-PINK--6-PCS: 0 in FBA, 20 inbound, 0.00/day, and the swap cannot load. The name would describe a child the campaign does not advertise.</t>
+          <t>Naming only.</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
